--- a/data/trans_orig/P19C07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>29620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26054</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49716</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453075</t>
+          <t>452074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468723</t>
+          <t>468909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>507870</t>
+          <t>508484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>525404</t>
+          <t>525677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>966225</t>
+          <t>965531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>989887</t>
+          <t>990694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39578</t>
+          <t>40140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38259</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66689</t>
+          <t>67142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>682550</t>
+          <t>681988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>703724</t>
+          <t>703496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>771495</t>
+          <t>770219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>789634</t>
+          <t>790167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1459665</t>
+          <t>1459212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1488095</t>
+          <t>1487608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26287</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51220</t>
+          <t>53091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517656</t>
+          <t>517603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534382</t>
+          <t>534110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553775</t>
+          <t>553607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>572403</t>
+          <t>572683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1078478</t>
+          <t>1076607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1103411</t>
+          <t>1102305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33915</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71546</t>
+          <t>69415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>675773</t>
+          <t>677117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694837</t>
+          <t>694805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>769058</t>
+          <t>768313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>791566</t>
+          <t>791324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1452140</t>
+          <t>1454271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1482362</t>
+          <t>1482000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66285</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103953</t>
+          <t>104631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117081</t>
+          <t>115636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>208510</t>
+          <t>205090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2350789</t>
+          <t>2350111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2388457</t>
+          <t>2387772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2623856</t>
+          <t>2625301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2663410</t>
+          <t>2663885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4987169</t>
+          <t>4990589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5039610</t>
+          <t>5041611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57583</t>
+          <t>57484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>574752</t>
+          <t>573737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>592524</t>
+          <t>592135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>603700</t>
+          <t>604016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>621054</t>
+          <t>622347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184169</t>
+          <t>1184268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1209742</t>
+          <t>1210416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37290</t>
+          <t>37245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56909</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>49382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85982</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>829708</t>
+          <t>829753</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>851875</t>
+          <t>851573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>841914</t>
+          <t>843761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>869169</t>
+          <t>870429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1679839</t>
+          <t>1683701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1716439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>24421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26811</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52436</t>
+          <t>52215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601924</t>
+          <t>601374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621244</t>
+          <t>621826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653476</t>
+          <t>654076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670076</t>
+          <t>670323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262093</t>
+          <t>1262314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287718</t>
+          <t>1288593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40891</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25029</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47588</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81080</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>764785</t>
+          <t>762979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>787050</t>
+          <t>786268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885613</t>
+          <t>884174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>908172</t>
+          <t>908377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1657797</t>
+          <t>1659122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1688968</t>
+          <t>1689547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78057</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117722</t>
+          <t>118212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92956</t>
+          <t>92424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137195</t>
+          <t>134191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183513</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240628</t>
+          <t>240083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2796937</t>
+          <t>2796447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2836602</t>
+          <t>2835812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3009126</t>
+          <t>3012130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3053365</t>
+          <t>3053897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5820352</t>
+          <t>5820897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5877467</t>
+          <t>5880663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38162</t>
+          <t>38067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>502076</t>
+          <t>503096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>516844</t>
+          <t>516859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>506201</t>
+          <t>506296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>526338</t>
+          <t>525911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1014674</t>
+          <t>1016164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1039153</t>
+          <t>1039779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43387</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>40605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44474</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75743</t>
+          <t>75249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>772959</t>
+          <t>774208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>796436</t>
+          <t>796782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>826828</t>
+          <t>825768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>846791</t>
+          <t>846606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1606976</t>
+          <t>1607470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1638245</t>
+          <t>1639202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48536</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529873</t>
+          <t>529938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543346</t>
+          <t>544254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>545263</t>
+          <t>545569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>565110</t>
+          <t>565367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1081562</t>
+          <t>1081929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1105437</t>
+          <t>1104911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32588</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61769</t>
+          <t>59823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>743252</t>
+          <t>742199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>760203</t>
+          <t>760626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>840383</t>
+          <t>840545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>860343</t>
+          <t>860991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1587707</t>
+          <t>1589653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1616888</t>
+          <t>1617883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>57493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96885</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>84665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123999</t>
+          <t>123209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153420</t>
+          <t>152832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205803</t>
+          <t>211060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2567448</t>
+          <t>2570581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2604758</t>
+          <t>2606840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2743316</t>
+          <t>2744106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2783271</t>
+          <t>2782650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5325845</t>
+          <t>5320588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5378228</t>
+          <t>5378816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46106</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35781</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>74445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>565198</t>
+          <t>564157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>595677</t>
+          <t>596071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616698</t>
+          <t>616170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>635659</t>
+          <t>635928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1190185</t>
+          <t>1188391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1227055</t>
+          <t>1226981</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>43273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>47406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37635</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80327</t>
+          <t>80645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1122535</t>
+          <t>1123443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1154769</t>
+          <t>1154554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>895169</t>
+          <t>894919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>917859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2028713</t>
+          <t>2028395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2071405</t>
+          <t>2071787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53120</t>
+          <t>54164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17380</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>60056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>46590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99751</t>
+          <t>99656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633147</t>
+          <t>632103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661856</t>
+          <t>661848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>863741</t>
+          <t>861997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>904673</t>
+          <t>902158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1508569</t>
+          <t>1508664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1562398</t>
+          <t>1561730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55490</t>
+          <t>57521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79693</t>
+          <t>79911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>857906</t>
+          <t>857442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877628</t>
+          <t>877832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007427</t>
+          <t>1005396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034722</t>
+          <t>1034246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873158</t>
+          <t>1872940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907866</t>
+          <t>1907642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80315</t>
+          <t>78717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140899</t>
+          <t>138984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>109933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>165198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202167</t>
+          <t>205341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290346</t>
+          <t>288038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3213322</t>
+          <t>3215237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273906</t>
+          <t>3275504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3410711</t>
+          <t>3413629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3466776</t>
+          <t>3468894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6642702</t>
+          <t>6645010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6730881</t>
+          <t>6727707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25763</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>48443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452074</t>
+          <t>452463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468909</t>
+          <t>468025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>508484</t>
+          <t>508498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>525677</t>
+          <t>525269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>965531</t>
+          <t>967498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>990694</t>
+          <t>989498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40140</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34007</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67142</t>
+          <t>67070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681988</t>
+          <t>679956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>703496</t>
+          <t>702925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>770219</t>
+          <t>771144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>790167</t>
+          <t>789112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1459212</t>
+          <t>1459284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1487608</t>
+          <t>1488111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>26649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>50513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517603</t>
+          <t>518440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534110</t>
+          <t>534529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553607</t>
+          <t>553641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>572683</t>
+          <t>571825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076607</t>
+          <t>1079185</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102305</t>
+          <t>1103328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45685</t>
+          <t>46928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69415</t>
+          <t>71738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677117</t>
+          <t>677743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694805</t>
+          <t>695467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>768313</t>
+          <t>767070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>791324</t>
+          <t>791749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1454271</t>
+          <t>1451948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1482000</t>
+          <t>1481943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66970</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104631</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115636</t>
+          <t>115038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205090</t>
+          <t>207455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2350111</t>
+          <t>2351410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2387772</t>
+          <t>2387395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2625301</t>
+          <t>2625899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2663885</t>
+          <t>2662803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4990589</t>
+          <t>4988224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5041611</t>
+          <t>5042696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>56797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>573737</t>
+          <t>573517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>592135</t>
+          <t>592114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>604016</t>
+          <t>604574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>622347</t>
+          <t>621608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184268</t>
+          <t>1184955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1210416</t>
+          <t>1210145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>37839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55062</t>
+          <t>56043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49382</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>829753</t>
+          <t>829159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>851573</t>
+          <t>851138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>843761</t>
+          <t>842780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>870429</t>
+          <t>869901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1683701</t>
+          <t>1680857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1716439</t>
+          <t>1715210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601374</t>
+          <t>600951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621826</t>
+          <t>621183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654076</t>
+          <t>653806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670323</t>
+          <t>670282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262314</t>
+          <t>1263277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288593</t>
+          <t>1289048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,49 +3724,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>35185</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>25031</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>49481</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35185</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24824</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>49027</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>61</t>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49330</t>
+          <t>49593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79755</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>762979</t>
+          <t>764619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>786268</t>
+          <t>786331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,47 +3837,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>94,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>898016</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>883720</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>908170</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>94,7%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>898016</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>884174</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>908377</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1659122</t>
+          <t>1657135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1689547</t>
+          <t>1689284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>79376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118212</t>
+          <t>119741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92424</t>
+          <t>93902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134191</t>
+          <t>138327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180317</t>
+          <t>181344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240083</t>
+          <t>239580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2796447</t>
+          <t>2794918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2835812</t>
+          <t>2835283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3012130</t>
+          <t>3007994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3053897</t>
+          <t>3052419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5820897</t>
+          <t>5821400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5880663</t>
+          <t>5879636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38067</t>
+          <t>39566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>53819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>503096</t>
+          <t>501623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>516859</t>
+          <t>516849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>506296</t>
+          <t>504797</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>525911</t>
+          <t>526200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1016164</t>
+          <t>1015537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1039779</t>
+          <t>1039326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>39669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75249</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>774208</t>
+          <t>773144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>796782</t>
+          <t>796406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>825768</t>
+          <t>826704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>846606</t>
+          <t>846413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1607470</t>
+          <t>1608726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1639202</t>
+          <t>1638845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>47818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529938</t>
+          <t>529876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544254</t>
+          <t>543470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>545569</t>
+          <t>545257</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>565367</t>
+          <t>565397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1081929</t>
+          <t>1082280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1104911</t>
+          <t>1105741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>58828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>742199</t>
+          <t>743385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>760626</t>
+          <t>760263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>840545</t>
+          <t>840873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>861181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1589653</t>
+          <t>1590648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1617883</t>
+          <t>1617896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>94876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84665</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123209</t>
+          <t>121465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>153503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211060</t>
+          <t>208873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2570581</t>
+          <t>2569457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2606840</t>
+          <t>2604197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2744106</t>
+          <t>2745850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2782650</t>
+          <t>2784939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5320588</t>
+          <t>5322775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5378816</t>
+          <t>5378145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47147</t>
+          <t>43282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>37090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74445</t>
+          <t>71482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>584528</t>
+          <t>632720</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564157</t>
+          <t>616249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>596071</t>
+          <t>642615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>627987</t>
+          <t>681560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616170</t>
+          <t>669309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>635928</t>
+          <t>690197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1212515</t>
+          <t>1314280</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1188391</t>
+          <t>1294198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1226981</t>
+          <t>1328590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>39486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>26647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47406</t>
+          <t>50352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>60870</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37253</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80645</t>
+          <t>79132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1142338</t>
+          <t>991596</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1123443</t>
+          <t>976694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1154554</t>
+          <t>1001027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>907980</t>
+          <t>1011499</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894919</t>
+          <t>997432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>917859</t>
+          <t>1021137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2050317</t>
+          <t>2003094</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2028395</t>
+          <t>1984832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2071787</t>
+          <t>2017405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>43761</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54164</t>
+          <t>60586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40390</t>
+          <t>46210</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60056</t>
+          <t>60779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>89971</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46590</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99656</t>
+          <t>112734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>649795</t>
+          <t>730247</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632103</t>
+          <t>713422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661848</t>
+          <t>744507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>881663</t>
+          <t>749135</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>861997</t>
+          <t>734566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>902158</t>
+          <t>759876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1531458</t>
+          <t>1479382</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1508664</t>
+          <t>1456619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1561730</t>
+          <t>1496310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>36790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40078</t>
+          <t>45027</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28671</t>
+          <t>33717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57521</t>
+          <t>62681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>67685</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45209</t>
+          <t>51702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79911</t>
+          <t>89278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>870042</t>
+          <t>925300</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>857442</t>
+          <t>911169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877832</t>
+          <t>934118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1022839</t>
+          <t>1031143</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1005396</t>
+          <t>1013489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034246</t>
+          <t>1042453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1892879</t>
+          <t>1956444</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1872940</t>
+          <t>1934851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907642</t>
+          <t>1972427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>107520</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78717</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138984</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109933</t>
+          <t>127565</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165198</t>
+          <t>176936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>269926</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205341</t>
+          <t>235502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288038</t>
+          <t>308107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3246701</t>
+          <t>3279863</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3215237</t>
+          <t>3250082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3275504</t>
+          <t>3304349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3440469</t>
+          <t>3473337</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3413629</t>
+          <t>3448512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3468894</t>
+          <t>3497883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6687170</t>
+          <t>6753199</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6645010</t>
+          <t>6715018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6727707</t>
+          <t>6787623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
